--- a/bindings/excel/examples/context_pricing_example.xlsx
+++ b/bindings/excel/examples/context_pricing_example.xlsx
@@ -33,7 +33,8 @@
     <definedName name="Context_Originations">'4 Results'!$F$7:$F$9</definedName>
     <definedName name="Context_Pricer">'3 Contracts'!$B$13</definedName>
     <definedName name="Context_PV">'4 Results'!$B$7</definedName>
-    <definedName name="Context_QuoteRows">'1 Inputs'!$A$18:$B$30</definedName>
+    <definedName name="Context_QuoteIds">'1 Inputs'!$A$18:$A$30</definedName>
+    <definedName name="Context_QuoteMid">'1 Inputs'!$D$17:$P$17</definedName>
     <definedName name="Context_Rate">'1 Inputs'!$B$11</definedName>
     <definedName name="Context_Risk">'4 Results'!$A$161</definedName>
     <definedName name="Context_Root">'2 Contexts'!$B$7</definedName>
@@ -240,7 +241,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Same quote levels, next business date.</t>
+          <t>Same independent quote arrays, next business date.</t>
         </r>
       </text>
     </comment>
@@ -439,7 +440,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>Mid</t>
+    <t>Mid levels: independent row array</t>
   </si>
   <si>
     <t>FixedRateDeposit_EUR_ESTR_1D</t>
@@ -505,13 +506,13 @@
     <t>Date, currency, base index and optional quote side.</t>
   </si>
   <si>
-    <t>Market quotes</t>
+    <t>Independent quote arrays</t>
   </si>
   <si>
     <t>Curve from matching quotes</t>
   </si>
   <si>
-    <t>Inputs is B12:B13. Both formulas use Root; neither references the previous addition. You may instead use ADD.CURVE(root,index,quote_table) in one cell.</t>
+    <t>Inputs is B12:B13. Both formulas use Root; neither references the previous addition. You may instead use ADD.CURVE(root,index,identifiers,mid) in one cell.</t>
   </si>
   <si>
     <t>Second dated root</t>
@@ -559,7 +560,7 @@
     <t>Capture next market</t>
   </si>
   <si>
-    <t>Same quote levels, next business date.</t>
+    <t>Same independent quote arrays, next business date.</t>
   </si>
   <si>
     <t>First snapshot</t>
@@ -1422,34 +1423,35 @@
     <tabColor rgb="FF337AB7"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="26.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="62.7109375" style="1" customWidth="1"/>
+    <col min="4" max="16" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38.25" customHeight="1">
+    <row r="1" spans="1:16" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="24" customHeight="1">
+    <row r="2" spans="1:16" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:3" ht="24" customHeight="1">
+    <row r="3" spans="1:16" ht="24" customHeight="1">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" spans="1:3" ht="36" customHeight="1">
+    <row r="4" spans="1:16" ht="36" customHeight="1">
       <c r="A4" s="6" t="s">
         <v>30</v>
       </c>
@@ -1457,7 +1459,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1">
+    <row r="6" spans="1:16" ht="36" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
@@ -1468,7 +1470,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="32.25" customHeight="1">
+    <row r="7" spans="1:16" ht="32.25" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>35</v>
       </c>
@@ -1479,7 +1481,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="32.25" customHeight="1">
+    <row r="8" spans="1:16" ht="32.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>38</v>
       </c>
@@ -1490,7 +1492,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="32.25" customHeight="1">
+    <row r="9" spans="1:16" ht="32.25" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -1501,7 +1503,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="32.25" customHeight="1">
+    <row r="10" spans="1:16" ht="32.25" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>44</v>
       </c>
@@ -1512,7 +1514,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="32.25" customHeight="1">
+    <row r="11" spans="1:16" ht="32.25" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>46</v>
       </c>
@@ -1523,7 +1525,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="32.25" customHeight="1">
+    <row r="12" spans="1:16" ht="32.25" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>48</v>
       </c>
@@ -1534,123 +1536,139 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="36" customHeight="1">
+    <row r="16" spans="1:16" ht="24" customHeight="1">
+      <c r="D16" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+    </row>
+    <row r="17" spans="1:16" ht="36" customHeight="1">
       <c r="A17" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>51</v>
-      </c>
+      <c r="B17" s="5"/>
       <c r="C17" s="5"/>
-    </row>
-    <row r="18" spans="1:3" ht="24" customHeight="1">
+      <c r="D17" s="12">
+        <v>0.029</v>
+      </c>
+      <c r="E17" s="12">
+        <v>0.0288</v>
+      </c>
+      <c r="F17" s="12">
+        <v>0.028</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0.0265</v>
+      </c>
+      <c r="H17" s="12">
+        <v>0.025</v>
+      </c>
+      <c r="I17" s="12">
+        <v>0.0245</v>
+      </c>
+      <c r="J17" s="12">
+        <v>0.0243</v>
+      </c>
+      <c r="K17" s="12">
+        <v>0.0242</v>
+      </c>
+      <c r="L17" s="12">
+        <v>0.0245</v>
+      </c>
+      <c r="M17" s="12">
+        <v>0.0252</v>
+      </c>
+      <c r="N17" s="12">
+        <v>0.0258</v>
+      </c>
+      <c r="O17" s="12">
+        <v>0.0255</v>
+      </c>
+      <c r="P17" s="12">
+        <v>0.024</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="24" customHeight="1">
       <c r="A18" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="12">
-        <v>0.029</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="24" customHeight="1">
+    </row>
+    <row r="19" spans="1:16" ht="24" customHeight="1">
       <c r="A19" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="12">
-        <v>0.0288</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="24" customHeight="1">
+    </row>
+    <row r="20" spans="1:16" ht="24" customHeight="1">
       <c r="A20" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="12">
-        <v>0.028</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="24" customHeight="1">
+    </row>
+    <row r="21" spans="1:16" ht="24" customHeight="1">
       <c r="A21" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="12">
-        <v>0.0265</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="24" customHeight="1">
+    </row>
+    <row r="22" spans="1:16" ht="24" customHeight="1">
       <c r="A22" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="12">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="24" customHeight="1">
+    </row>
+    <row r="23" spans="1:16" ht="24" customHeight="1">
       <c r="A23" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="12">
-        <v>0.0245</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="24" customHeight="1">
+    </row>
+    <row r="24" spans="1:16" ht="24" customHeight="1">
       <c r="A24" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="12">
-        <v>0.0243</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="24" customHeight="1">
+    </row>
+    <row r="25" spans="1:16" ht="24" customHeight="1">
       <c r="A25" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="12">
-        <v>0.0242</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="24" customHeight="1">
+    </row>
+    <row r="26" spans="1:16" ht="24" customHeight="1">
       <c r="A26" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="12">
-        <v>0.0245</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="24" customHeight="1">
+    </row>
+    <row r="27" spans="1:16" ht="24" customHeight="1">
       <c r="A27" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="12">
-        <v>0.0252</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="24" customHeight="1">
+    </row>
+    <row r="28" spans="1:16" ht="24" customHeight="1">
       <c r="A28" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="12">
-        <v>0.0258</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="24" customHeight="1">
+    </row>
+    <row r="29" spans="1:16" ht="24" customHeight="1">
       <c r="A29" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="12">
-        <v>0.0255</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="24" customHeight="1">
+    </row>
+    <row r="30" spans="1:16" ht="24" customHeight="1">
       <c r="A30" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="12">
-        <v>0.024</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C3"/>
+    <mergeCell ref="D16:P16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
@@ -1741,7 +1759,7 @@
         <v>73</v>
       </c>
       <c r="B12" s="10" cm="1" t="str">
-        <f t="array" ref="B12">_xll.QS.CONTEXT.ADD.QUOTES(Context_Root,Context_QuoteRows)</f>
+        <f t="array" ref="B12">_xll.QS.CONTEXT.ADD.QUOTES(Context_Root,Context_QuoteIds,Context_QuoteMid)</f>
         <v/>
       </c>
     </row>
@@ -1791,7 +1809,7 @@
         <v>78</v>
       </c>
       <c r="B24" s="10" cm="1" t="str">
-        <f t="array" ref="B24">_xll.QS.CONTEXT.ADD.CURVE(Context_NextRoot,"ESTR",Context_QuoteRows)</f>
+        <f t="array" ref="B24">_xll.QS.CONTEXT.ADD.CURVE(Context_NextRoot,"ESTR",Context_QuoteIds,Context_QuoteMid)</f>
         <v/>
       </c>
     </row>

--- a/bindings/excel/examples/context_pricing_example.xlsx
+++ b/bindings/excel/examples/context_pricing_example.xlsx
@@ -29,6 +29,7 @@
     <definedName name="Context_NextRoot">'2 Contexts'!$B$19</definedName>
     <definedName name="Context_NextSnapshot">'3 Contracts'!$B$19</definedName>
     <definedName name="Context_Notional">'1 Inputs'!$B$10</definedName>
+    <definedName name="Context_ObservationTimes">'3 Contracts'!$D$22:$D$23</definedName>
     <definedName name="Context_Options">'3 Contracts'!$B$7</definedName>
     <definedName name="Context_Originations">'4 Results'!$F$7:$F$9</definedName>
     <definedName name="Context_Pricer">'3 Contracts'!$B$13</definedName>
@@ -228,7 +229,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Captures market quotes and the curve definition together; fixings stay separate.</t>
+          <t>Complete context includes quotes and construction settings.</t>
         </r>
       </text>
     </comment>
@@ -241,7 +242,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Same independent quote arrays, next business date.</t>
+          <t>Next complete dated context.</t>
         </r>
       </text>
     </comment>
@@ -254,7 +255,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Historical batch pricing constructs each distinct selected market once.</t>
+          <t>Independent prepared-context and timestamp arrays.</t>
         </r>
       </text>
     </comment>
@@ -285,7 +286,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="112">
   <si>
     <t>Context-first pricing</t>
   </si>
@@ -551,28 +552,34 @@
     <t>An explicit discount curve with optional named refinancing and fair-rate settings.</t>
   </si>
   <si>
-    <t>Capture first market</t>
-  </si>
-  <si>
-    <t>Captures market quotes and the curve definition together; fixings stay separate.</t>
-  </si>
-  <si>
-    <t>Capture next market</t>
-  </si>
-  <si>
-    <t>Same independent quote arrays, next business date.</t>
-  </si>
-  <si>
-    <t>First snapshot</t>
-  </si>
-  <si>
-    <t>Second snapshot</t>
+    <t>Prepare first market</t>
+  </si>
+  <si>
+    <t>Complete context includes quotes and construction settings.</t>
+  </si>
+  <si>
+    <t>Prepare next market</t>
+  </si>
+  <si>
+    <t>Next complete dated context.</t>
+  </si>
+  <si>
+    <t>First context</t>
+  </si>
+  <si>
+    <t>Second context</t>
+  </si>
+  <si>
+    <t>2026-02-24T16:00:00Z</t>
+  </si>
+  <si>
+    <t>2026-02-25T16:00:00Z</t>
   </si>
   <si>
     <t>Archive complete markets</t>
   </si>
   <si>
-    <t>Historical batch pricing constructs each distinct selected market once.</t>
+    <t>Independent prepared-context and timestamp arrays.</t>
   </si>
   <si>
     <t>Direct prices and historical batch</t>
@@ -1146,7 +1153,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="26.25" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="26" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" style="1" customWidth="1"/>
@@ -1173,7 +1180,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" ht="26.25" customHeight="1">
+    <row r="3" spans="1:6" ht="26" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1183,7 +1190,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:6" ht="26.25" customHeight="1">
+    <row r="4" spans="1:6" ht="26" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1191,7 +1198,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
     </row>
-    <row r="6" spans="1:6" ht="26.25" customHeight="1">
+    <row r="6" spans="1:6" ht="26" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
@@ -1201,7 +1208,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" ht="26.25" customHeight="1">
+    <row r="7" spans="1:6" ht="26" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -1209,7 +1216,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="9" spans="1:6" ht="26.25" customHeight="1">
+    <row r="9" spans="1:6" ht="26" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>3</v>
       </c>
@@ -1219,7 +1226,7 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:6" ht="33.75" customHeight="1">
+    <row r="10" spans="1:6" ht="34" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>4</v>
       </c>
@@ -1233,7 +1240,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:6" ht="33.75" customHeight="1">
+    <row r="11" spans="1:6" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
@@ -1247,7 +1254,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:6" ht="33.75" customHeight="1">
+    <row r="12" spans="1:6" ht="34" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -1261,7 +1268,7 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:6" ht="33.75" customHeight="1">
+    <row r="13" spans="1:6" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
@@ -1275,7 +1282,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="16" spans="1:6" ht="26.25" customHeight="1">
+    <row r="16" spans="1:6" ht="26" customHeight="1">
       <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
@@ -1321,7 +1328,7 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
     </row>
-    <row r="21" spans="1:6" ht="26.25" customHeight="1">
+    <row r="21" spans="1:6" ht="26" customHeight="1">
       <c r="A21" s="5" t="s">
         <v>23</v>
       </c>
@@ -1331,7 +1338,7 @@
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
     </row>
-    <row r="22" spans="1:6" ht="33.75" customHeight="1">
+    <row r="22" spans="1:6" ht="34" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>24</v>
       </c>
@@ -1341,7 +1348,7 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:6" ht="33.75" customHeight="1">
+    <row r="23" spans="1:6" ht="34" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>25</v>
       </c>
@@ -1351,7 +1358,7 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" ht="33.75" customHeight="1">
+    <row r="24" spans="1:6" ht="34" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>26</v>
       </c>
@@ -1361,7 +1368,7 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
     </row>
-    <row r="26" spans="1:6" ht="26.25" customHeight="1">
+    <row r="26" spans="1:6" ht="26" customHeight="1">
       <c r="A26" s="7" t="s">
         <v>27</v>
       </c>
@@ -1371,7 +1378,7 @@
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:6" ht="26.25" customHeight="1">
+    <row r="27" spans="1:6" ht="26" customHeight="1">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -1432,7 +1439,7 @@
     <col min="4" max="16" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="38.25" customHeight="1">
+    <row r="1" spans="1:16" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
@@ -1470,7 +1477,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="32.25" customHeight="1">
+    <row r="7" spans="1:16" ht="32" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>35</v>
       </c>
@@ -1481,7 +1488,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="32.25" customHeight="1">
+    <row r="8" spans="1:16" ht="32" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>38</v>
       </c>
@@ -1492,7 +1499,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="32.25" customHeight="1">
+    <row r="9" spans="1:16" ht="32" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -1503,7 +1510,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="32.25" customHeight="1">
+    <row r="10" spans="1:16" ht="32" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>44</v>
       </c>
@@ -1514,7 +1521,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="32.25" customHeight="1">
+    <row r="11" spans="1:16" ht="32" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>46</v>
       </c>
@@ -1525,7 +1532,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="32.25" customHeight="1">
+    <row r="12" spans="1:16" ht="32" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>48</v>
       </c>
@@ -1696,7 +1703,7 @@
     <col min="2" max="3" width="48.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38.25" customHeight="1">
+    <row r="1" spans="1:3" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>65</v>
       </c>
@@ -1734,7 +1741,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="38.25" customHeight="1">
+    <row r="7" spans="1:3" ht="38" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>71</v>
       </c>
@@ -1746,7 +1753,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="33.75" customHeight="1">
+    <row r="8" spans="1:3" ht="34" customHeight="1">
       <c r="A8" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B7),",",", ")</f>
         <v>=QS.CONTEXT.CREATE("Example.Context", Context_Date, "EUR", "ESTR")</v>
@@ -1784,7 +1791,7 @@
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
     </row>
-    <row r="19" spans="1:3" ht="38.25" customHeight="1">
+    <row r="19" spans="1:3" ht="38" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>76</v>
       </c>
@@ -1796,7 +1803,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="33.75" customHeight="1">
+    <row r="20" spans="1:3" ht="34" customHeight="1">
       <c r="A20" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B19),",",", ")</f>
         <v>=QS.CONTEXT.CREATE("Example.Next", Context_NextDate, "EUR", "ESTR")</v>
@@ -1840,14 +1847,14 @@
     <tabColor rgb="FF78909C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.7109375" style="1" customWidth="1"/>
     <col min="2" max="3" width="48.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38.25" customHeight="1">
+    <row r="1" spans="1:3" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>79</v>
       </c>
@@ -1885,7 +1892,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="38.25" customHeight="1">
+    <row r="7" spans="1:3" ht="38" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>82</v>
       </c>
@@ -1897,7 +1904,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="33.75" customHeight="1">
+    <row r="8" spans="1:3" ht="34" customHeight="1">
       <c r="A8" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B7),",",", ")</f>
         <v>=QS.LOAN.SETTINGS("Example.Options", Context_Balloon)</v>
@@ -1905,7 +1912,7 @@
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
     </row>
-    <row r="10" spans="1:3" ht="38.25" customHeight="1">
+    <row r="10" spans="1:3" ht="38" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>84</v>
       </c>
@@ -1917,7 +1924,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="33.75" customHeight="1">
+    <row r="11" spans="1:3" ht="34" customHeight="1">
       <c r="A11" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B10),",",", ")</f>
         <v>=QS.INSTRUMENT.LOAN("Example.Loan", Context_Date, Context_Maturity, "EUR", Context_Notional, Context_Rate, , "Balloon", "Monthly", "Actual365", Context_Options)</v>
@@ -1925,7 +1932,7 @@
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
     </row>
-    <row r="13" spans="1:3" ht="38.25" customHeight="1">
+    <row r="13" spans="1:3" ht="38" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>86</v>
       </c>
@@ -1937,7 +1944,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="33.75" customHeight="1">
+    <row r="14" spans="1:3" ht="34" customHeight="1">
       <c r="A14" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B13),",",", ")</f>
         <v>=QS.LOAN.PRICER("Example.Pricer", "EUR", "ESTR")</v>
@@ -1945,47 +1952,47 @@
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
     </row>
-    <row r="16" spans="1:3" ht="38.25" customHeight="1">
+    <row r="16" spans="1:3" ht="38" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>88</v>
       </c>
       <c r="B16" s="10" cm="1" t="str">
-        <f t="array" ref="B16">_xll.QS.SNAPSHOT.FROM.CONTEXT("Example.Snapshot","2026-02-24T16:00:00Z",Context_Root,Context_Inputs)</f>
+        <f t="array" ref="B16">_xll.QS.CONTEXT.PREPARE("Example.Market",Context_Root,Context_Inputs)</f>
         <v/>
       </c>
       <c r="C16" s="7" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="33.75" customHeight="1">
+    <row r="17" spans="1:4" ht="34" customHeight="1">
       <c r="A17" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B16),",",", ")</f>
-        <v>=QS.SNAPSHOT.FROM.CONTEXT("Example.Snapshot", "2026-02-24T16:00:00Z", Context_Root, Context_Inputs)</v>
+        <v>=QS.CONTEXT.PREPARE("Example.Market", Context_Root, Context_Inputs)</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
     </row>
-    <row r="19" spans="1:3" ht="38.25" customHeight="1">
+    <row r="19" spans="1:4" ht="38" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>90</v>
       </c>
       <c r="B19" s="10" cm="1" t="str">
-        <f t="array" ref="B19">_xll.QS.SNAPSHOT.FROM.CONTEXT("Example.NextSnapshot","2026-02-25T16:00:00Z",Context_NextRoot,Context_NextInputs)</f>
+        <f t="array" ref="B19">_xll.QS.CONTEXT.PREPARE("Example.NextMarket",Context_NextRoot,Context_NextInputs)</f>
         <v/>
       </c>
       <c r="C19" s="7" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="33.75" customHeight="1">
+    <row r="20" spans="1:4" ht="34" customHeight="1">
       <c r="A20" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B19),",",", ")</f>
-        <v>=QS.SNAPSHOT.FROM.CONTEXT("Example.NextSnapshot", "2026-02-25T16:00:00Z", Context_NextRoot, Context_NextInputs)</v>
+        <v>=QS.CONTEXT.PREPARE("Example.NextMarket", Context_NextRoot, Context_NextInputs)</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
     </row>
-    <row r="22" spans="1:3" ht="24" customHeight="1">
+    <row r="22" spans="1:4" ht="24" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>92</v>
       </c>
@@ -1993,8 +2000,11 @@
         <f>Context_Snapshot</f>
         <v/>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="24" customHeight="1">
+      <c r="D22" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="24" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>93</v>
       </c>
@@ -2002,23 +2012,26 @@
         <f>Context_NextSnapshot</f>
         <v/>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="38.25" customHeight="1">
+      <c r="D23" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="38" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B25" s="10" cm="1" t="str">
-        <f t="array" ref="B25">_xll.QS.SNAPSHOTS.CREATE("Example.Archive",Context_Snapshots)</f>
+        <f t="array" ref="B25">_xll.QS.SNAPSHOT.FROM.RANGE("Example.Archive",Context_Snapshots,Context_ObservationTimes)</f>
         <v/>
       </c>
       <c r="C25" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="33.75" customHeight="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="34" customHeight="1">
       <c r="A26" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B25),",",", ")</f>
-        <v>=QS.SNAPSHOTS.CREATE("Example.Archive", Context_Snapshots)</v>
+        <v>=QS.SNAPSHOT.FROM.RANGE("Example.Archive", Context_Snapshots, Context_ObservationTimes)</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
@@ -2065,9 +2078,9 @@
     <col min="7" max="7" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="38.25" customHeight="1">
+    <row r="1" spans="1:7" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2078,7 +2091,7 @@
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2103,7 +2116,7 @@
     </row>
     <row r="6" spans="1:7" ht="36" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>33</v>
@@ -2112,44 +2125,44 @@
         <v>34</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="24" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B7" s="14" cm="1" t="str">
-        <f t="array" ref="B7">_xll.QS.CONTEXT.PRICE(Context_Root,Context_Loan,"Value",Context_Inputs)</f>
+        <f t="array" ref="B7">_xll.QS.EVALUATE(Context_Root,Context_Loan,"Value",Context_Inputs)</f>
         <v/>
       </c>
       <c r="C7" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E7" s="10">
         <f>Context_Loan</f>
         <v/>
       </c>
       <c r="F7" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G7" s="14" cm="1" t="str">
-        <f t="array" ref="G7">_xll.QS.HISTORY.VALUES(Context_Archive,Context_HistoryInstruments,Context_Originations,Context_Pricer)</f>
+        <f t="array" ref="G7">_xll.QS.EVALUATE.FROM.SNAPSHOT(Context_Archive,Context_HistoryInstruments,Context_Originations,Context_Pricer)</f>
         <v/>
       </c>
     </row>
     <row r="8" spans="1:7" ht="24" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B8" s="15" cm="1" t="str">
-        <f t="array" ref="B8">_xll.QS.CONTEXT.PRICE(Context_Root,Context_Loan,"FairRate(0)",Context_Inputs,Context_Pricer)</f>
+        <f t="array" ref="B8">_xll.QS.EVALUATE(Context_Root,Context_Loan,"FairRate(0)",Context_Inputs,Context_Pricer)</f>
         <v/>
       </c>
       <c r="E8" s="10">
@@ -2157,7 +2170,7 @@
         <v/>
       </c>
       <c r="F8" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="24" customHeight="1">
@@ -2166,28 +2179,28 @@
         <v/>
       </c>
       <c r="F9" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="24" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="24" customHeight="1">
       <c r="A13" s="9" cm="1" t="str">
-        <f t="array" ref="A13">_xll.QS.CONTEXT.PRICE(Context_Root,Context_Loan,"Cashflows",Context_Inputs)</f>
+        <f t="array" ref="A13">_xll.QS.EVALUATE(Context_Root,Context_Loan,"Cashflows",Context_Inputs)</f>
         <v/>
       </c>
     </row>
     <row r="160" spans="1:1" ht="24" customHeight="1">
       <c r="A160" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="161" spans="1:1" ht="24" customHeight="1">
       <c r="A161" s="9" cm="1" t="str">
-        <f t="array" ref="A161">_xll.QS.CONTEXT.PRICE(Context_Root,Context_Loan,"Sensitivities",Context_Inputs)</f>
+        <f t="array" ref="A161">_xll.QS.EVALUATE(Context_Root,Context_Loan,"Sensitivities",Context_Inputs)</f>
         <v/>
       </c>
     </row>
